--- a/Packages/cn.etetet.startconfig/Excel/StartConfig/Example/StartSceneConfig@s.xlsx
+++ b/Packages/cn.etetet.startconfig/Excel/StartConfig/Example/StartSceneConfig@s.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20452" windowHeight="8707" activeTab="2"/>
+    <workbookView windowWidth="25600" windowHeight="10480" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Router" sheetId="3" r:id="rId1"/>
     <sheet name="Realm" sheetId="4" r:id="rId2"/>
     <sheet name="Game" sheetId="1" r:id="rId3"/>
+    <sheet name="公共服" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="29">
   <si>
     <t>Id</t>
   </si>
@@ -113,6 +114,9 @@
   </si>
   <si>
     <t>Map2</t>
+  </si>
+  <si>
+    <t>LoginCenter</t>
   </si>
 </sst>
 </file>
@@ -1109,17 +1113,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C3:H10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="21.1238938053097" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7522123893805" style="1" customWidth="1"/>
-    <col min="3" max="5" width="12.6283185840708" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.3716814159292" style="2" customWidth="1"/>
-    <col min="7" max="8" width="13.1238938053097" style="2" customWidth="1"/>
+    <col min="1" max="1" width="21.1272727272727" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7545454545455" style="1" customWidth="1"/>
+    <col min="3" max="5" width="12.6272727272727" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.3727272727273" style="2" customWidth="1"/>
+    <col min="7" max="8" width="13.1272727272727" style="2" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:8">
+    <row r="3" ht="13.5" spans="3:8">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1139,7 +1143,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="3:8">
+    <row r="4" ht="13.5" spans="3:8">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -1159,7 +1163,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="3:8">
+    <row r="5" ht="13.5" spans="3:8">
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
@@ -1290,7 +1294,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9.02727272727273" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -1387,17 +1391,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C3:H10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="21.1238938053097" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7522123893805" style="1" customWidth="1"/>
-    <col min="3" max="5" width="12.6283185840708" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.3716814159292" style="2" customWidth="1"/>
-    <col min="7" max="8" width="13.1238938053097" style="2" customWidth="1"/>
+    <col min="1" max="1" width="21.1272727272727" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7545454545455" style="1" customWidth="1"/>
+    <col min="3" max="5" width="12.6272727272727" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.3727272727273" style="2" customWidth="1"/>
+    <col min="7" max="8" width="13.1272727272727" style="2" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:8">
+    <row r="3" ht="13.5" spans="3:8">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1417,7 +1421,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="3:8">
+    <row r="4" ht="13.5" spans="3:8">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -1437,7 +1441,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="3:8">
+    <row r="5" ht="13.5" spans="3:8">
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
@@ -1457,7 +1461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" customFormat="1" ht="13.5" spans="3:8">
+    <row r="6" customFormat="1" ht="14" spans="3:8">
       <c r="C6" s="4">
         <v>301</v>
       </c>
@@ -1556,4 +1560,163 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
+  <cols>
+    <col min="6" max="7" width="11.1818181818182" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8">
+      <c r="C6" s="4">
+        <v>401</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1000</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Packages/cn.etetet.startconfig/Excel/StartConfig/Example/StartSceneConfig@s.xlsx
+++ b/Packages/cn.etetet.startconfig/Excel/StartConfig/Example/StartSceneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Router" sheetId="3" r:id="rId1"/>
@@ -1113,17 +1113,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C3:H10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="21.1272727272727" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7545454545455" style="1" customWidth="1"/>
-    <col min="3" max="5" width="12.6272727272727" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.3727272727273" style="2" customWidth="1"/>
-    <col min="7" max="8" width="13.1272727272727" style="2" customWidth="1"/>
+    <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7583333333333" style="1" customWidth="1"/>
+    <col min="3" max="5" width="12.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.375" style="2" customWidth="1"/>
+    <col min="7" max="8" width="13.125" style="2" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="13.5" spans="3:8">
+    <row r="3" spans="3:8">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="13.5" spans="3:8">
+    <row r="4" spans="3:8">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="13.5" spans="3:8">
+    <row r="5" spans="3:8">
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
@@ -1294,14 +1294,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="9.02727272727273" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9.025" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="3:8">
+    <row r="3" ht="14.25" spans="3:8">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="3:8">
+    <row r="4" ht="14.25" spans="3:8">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="3:8">
+    <row r="5" ht="14.25" spans="3:8">
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="3:8">
+    <row r="6" ht="14.25" spans="3:8">
       <c r="C6" s="4">
         <v>201</v>
       </c>
@@ -1391,17 +1391,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C3:H10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="21.1272727272727" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7545454545455" style="1" customWidth="1"/>
-    <col min="3" max="5" width="12.6272727272727" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.3727272727273" style="2" customWidth="1"/>
-    <col min="7" max="8" width="13.1272727272727" style="2" customWidth="1"/>
+    <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7583333333333" style="1" customWidth="1"/>
+    <col min="3" max="5" width="12.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.375" style="2" customWidth="1"/>
+    <col min="7" max="8" width="13.125" style="2" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="13.5" spans="3:8">
+    <row r="3" spans="3:8">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="13.5" spans="3:8">
+    <row r="4" spans="3:8">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="13.5" spans="3:8">
+    <row r="5" spans="3:8">
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" customFormat="1" ht="14" spans="3:8">
+    <row r="6" customFormat="1" spans="3:8">
       <c r="C6" s="4">
         <v>301</v>
       </c>
@@ -1566,12 +1566,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="6" max="7" width="11.1818181818182" customWidth="1"/>
+    <col min="6" max="7" width="11.1833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" ht="14.25" spans="1:8">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
@@ -1581,7 +1581,7 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" ht="14.25" spans="1:8">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2"/>
@@ -1591,7 +1591,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" ht="14.25" spans="1:8">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="3" t="s">
@@ -1613,7 +1613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" ht="14.25" spans="1:8">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="3" t="s">
@@ -1635,7 +1635,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" ht="14.25" spans="1:8">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="3" t="s">
@@ -1657,7 +1657,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="3:8">
+    <row r="6" ht="14.25" spans="3:8">
       <c r="C6" s="4">
         <v>401</v>
       </c>
@@ -1673,9 +1673,11 @@
       <c r="G6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="H6" s="4">
+        <v>40101</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" spans="1:8">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="4"/>
@@ -1685,7 +1687,7 @@
       <c r="G7" s="2"/>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" ht="14.25" spans="1:8">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="4"/>
@@ -1695,7 +1697,7 @@
       <c r="G8" s="2"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" ht="14.25" spans="1:8">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="4"/>
@@ -1705,7 +1707,7 @@
       <c r="G9" s="2"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" ht="14.25" spans="1:8">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="4"/>
